--- a/ml_results/cv_bookkeeper.xlsx
+++ b/ml_results/cv_bookkeeper.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\denni\Desktop\Grafici BookKeeper\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\denni\isw2\project-analyzer\ml_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BAA206-2989-41AA-AAEF-A168F2EF086E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59BBE3A-9261-4D93-91EC-B8FD35F16482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
